--- a/output/casestudy_20260904.xlsx
+++ b/output/casestudy_20260904.xlsx
@@ -544,7 +544,7 @@
         </is>
       </c>
       <c r="N2" t="n">
-        <v>8.211337299999286</v>
+        <v>9.956445199999507</v>
       </c>
     </row>
     <row r="3">
@@ -596,7 +596,7 @@
         </is>
       </c>
       <c r="N3" t="n">
-        <v>8.509379800000715</v>
+        <v>10.60526969999955</v>
       </c>
     </row>
     <row r="4">
@@ -648,7 +648,7 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>4.867189499999768</v>
+        <v>6.607076600001164</v>
       </c>
     </row>
     <row r="5">
@@ -700,7 +700,7 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>8.30324759999985</v>
+        <v>11.42244089999986</v>
       </c>
     </row>
     <row r="6">
@@ -752,7 +752,7 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>8.876309799999945</v>
+        <v>12.46239680000144</v>
       </c>
     </row>
     <row r="7">
@@ -804,7 +804,7 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>5.549197500000446</v>
+        <v>8.244606000000203</v>
       </c>
     </row>
     <row r="8">
@@ -856,7 +856,7 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>10.63354789999994</v>
+        <v>13.43888209999932</v>
       </c>
     </row>
   </sheetData>
@@ -7193,7 +7193,7 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>69546898.36799997</v>
+        <v>72647491.26799998</v>
       </c>
       <c r="D28" t="inlineStr"/>
       <c r="E28" t="inlineStr">
@@ -9275,7 +9275,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>8.2 초</t>
+          <t>10.0 초</t>
         </is>
       </c>
     </row>
@@ -9287,7 +9287,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>8.5 초</t>
+          <t>10.6 초</t>
         </is>
       </c>
     </row>
@@ -9299,7 +9299,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>4.9 초</t>
+          <t>6.6 초</t>
         </is>
       </c>
     </row>
@@ -9311,7 +9311,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>8.3 초</t>
+          <t>11.4 초</t>
         </is>
       </c>
     </row>
@@ -9323,7 +9323,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>8.9 초</t>
+          <t>12.5 초</t>
         </is>
       </c>
     </row>
@@ -9335,7 +9335,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>5.5 초</t>
+          <t>8.2 초</t>
         </is>
       </c>
     </row>
@@ -9347,7 +9347,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>10.6 초</t>
+          <t>13.4 초</t>
         </is>
       </c>
     </row>
@@ -9359,7 +9359,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>57.9 초</t>
+          <t>76.9 초</t>
         </is>
       </c>
     </row>

--- a/output/casestudy_20260904.xlsx
+++ b/output/casestudy_20260904.xlsx
@@ -544,7 +544,7 @@
         </is>
       </c>
       <c r="N2" t="n">
-        <v>9.956445199999507</v>
+        <v>8.039452099998016</v>
       </c>
     </row>
     <row r="3">
@@ -596,7 +596,7 @@
         </is>
       </c>
       <c r="N3" t="n">
-        <v>10.60526969999955</v>
+        <v>8.07454560000042</v>
       </c>
     </row>
     <row r="4">
@@ -648,7 +648,7 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>6.607076600001164</v>
+        <v>4.756771899999876</v>
       </c>
     </row>
     <row r="5">
@@ -700,7 +700,7 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>11.42244089999986</v>
+        <v>8.44309869999779</v>
       </c>
     </row>
     <row r="6">
@@ -752,7 +752,7 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>12.46239680000144</v>
+        <v>8.868273000000045</v>
       </c>
     </row>
     <row r="7">
@@ -804,7 +804,7 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>8.244606000000203</v>
+        <v>5.740751500001352</v>
       </c>
     </row>
     <row r="8">
@@ -856,7 +856,7 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>13.43888209999932</v>
+        <v>11.32262450000053</v>
       </c>
     </row>
   </sheetData>
@@ -7193,7 +7193,7 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>72647491.26799998</v>
+        <v>28375570.36800003</v>
       </c>
       <c r="D28" t="inlineStr"/>
       <c r="E28" t="inlineStr">
@@ -9275,7 +9275,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>10.0 초</t>
+          <t>8.0 초</t>
         </is>
       </c>
     </row>
@@ -9287,7 +9287,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>10.6 초</t>
+          <t>8.1 초</t>
         </is>
       </c>
     </row>
@@ -9299,7 +9299,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>6.6 초</t>
+          <t>4.8 초</t>
         </is>
       </c>
     </row>
@@ -9311,7 +9311,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>11.4 초</t>
+          <t>8.4 초</t>
         </is>
       </c>
     </row>
@@ -9323,7 +9323,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>12.5 초</t>
+          <t>8.9 초</t>
         </is>
       </c>
     </row>
@@ -9335,7 +9335,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>8.2 초</t>
+          <t>5.7 초</t>
         </is>
       </c>
     </row>
@@ -9347,7 +9347,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>13.4 초</t>
+          <t>11.3 초</t>
         </is>
       </c>
     </row>
@@ -9359,7 +9359,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>76.9 초</t>
+          <t>58.3 초</t>
         </is>
       </c>
     </row>

--- a/output/casestudy_20260904.xlsx
+++ b/output/casestudy_20260904.xlsx
@@ -544,7 +544,7 @@
         </is>
       </c>
       <c r="N2" t="n">
-        <v>8.039452099998016</v>
+        <v>8.009656800000812</v>
       </c>
     </row>
     <row r="3">
@@ -596,7 +596,7 @@
         </is>
       </c>
       <c r="N3" t="n">
-        <v>8.07454560000042</v>
+        <v>7.90053959999932</v>
       </c>
     </row>
     <row r="4">
@@ -648,7 +648,7 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>4.756771899999876</v>
+        <v>4.712594500000705</v>
       </c>
     </row>
     <row r="5">
@@ -700,7 +700,7 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>8.44309869999779</v>
+        <v>8.214937499997177</v>
       </c>
     </row>
     <row r="6">
@@ -752,7 +752,7 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>8.868273000000045</v>
+        <v>8.76685709999947</v>
       </c>
     </row>
     <row r="7">
@@ -778,7 +778,7 @@
         <v>10920.64</v>
       </c>
       <c r="F7" t="n">
-        <v>2801</v>
+        <v>3603.8112</v>
       </c>
       <c r="G7" t="n">
         <v>23.75842547228519</v>
@@ -787,16 +787,16 @@
         <v>257.8965090732941</v>
       </c>
       <c r="I7" t="n">
-        <v>239586711.1</v>
+        <v>312234202.368</v>
       </c>
       <c r="J7" t="n">
         <v>2522534959.357</v>
       </c>
       <c r="K7" t="n">
-        <v>2762121670.457</v>
+        <v>2834769161.725</v>
       </c>
       <c r="L7" t="n">
-        <v>8.674010043169449</v>
+        <v>11.01444895703609</v>
       </c>
       <c r="M7" t="inlineStr">
         <is>
@@ -804,7 +804,7 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>5.740751500001352</v>
+        <v>5.599225300000398</v>
       </c>
     </row>
     <row r="8">
@@ -856,7 +856,7 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>11.32262450000053</v>
+        <v>10.74190250000174</v>
       </c>
     </row>
   </sheetData>
@@ -1587,7 +1587,7 @@
         <v>0</v>
       </c>
       <c r="F22" t="n">
-        <v>2801</v>
+        <v>3603.8112</v>
       </c>
       <c r="G22" t="n">
         <v>0</v>
@@ -1618,19 +1618,19 @@
         <v>0</v>
       </c>
       <c r="F23" t="n">
-        <v>2732.308927852665</v>
+        <v>3603.8112</v>
       </c>
       <c r="G23" t="n">
-        <v>9198978.795016408</v>
+        <v>0</v>
       </c>
       <c r="H23" t="n">
         <v>78883246.71788645</v>
       </c>
       <c r="I23" t="n">
-        <v>88082225.51290274</v>
+        <v>78883246.71788645</v>
       </c>
       <c r="J23" t="n">
-        <v>88082225.51290274</v>
+        <v>78883246.71788645</v>
       </c>
       <c r="K23" t="inlineStr"/>
       <c r="L23" t="inlineStr"/>
@@ -1649,19 +1649,19 @@
         <v>102.5920444029124</v>
       </c>
       <c r="F24" t="n">
-        <v>2715.53785570533</v>
+        <v>3603.8112</v>
       </c>
       <c r="G24" t="n">
-        <v>11238788.15785098</v>
+        <v>0</v>
       </c>
       <c r="H24" t="n">
         <v>157756972.8940516</v>
       </c>
       <c r="I24" t="n">
-        <v>168995761.0519023</v>
+        <v>157756972.8940516</v>
       </c>
       <c r="J24" t="n">
-        <v>168995761.0519023</v>
+        <v>157756972.8940516</v>
       </c>
       <c r="K24" t="inlineStr"/>
       <c r="L24" t="inlineStr"/>
@@ -1680,19 +1680,19 @@
         <v>68551.64897212535</v>
       </c>
       <c r="F25" t="n">
-        <v>2701.871477154071</v>
+        <v>3603.8112</v>
       </c>
       <c r="G25" t="n">
-        <v>14666364.50237396</v>
+        <v>0</v>
       </c>
       <c r="H25" t="n">
         <v>308458353.0788054</v>
       </c>
       <c r="I25" t="n">
-        <v>323124717.5811791</v>
+        <v>308458353.0788054</v>
       </c>
       <c r="J25" t="n">
-        <v>323124717.5811791</v>
+        <v>308458353.0788054</v>
       </c>
       <c r="K25" t="inlineStr"/>
       <c r="L25" t="inlineStr"/>
@@ -1748,16 +1748,16 @@
         <v>120.48</v>
       </c>
       <c r="G27" t="n">
-        <v>1381815.952363797</v>
+        <v>1360265.698040357</v>
       </c>
       <c r="H27" t="n">
         <v>21832794.0374309</v>
       </c>
       <c r="I27" t="n">
-        <v>23214609.9897947</v>
+        <v>23193059.73547126</v>
       </c>
       <c r="J27" t="n">
-        <v>23214609.9897947</v>
+        <v>23193059.73547126</v>
       </c>
       <c r="K27" t="inlineStr"/>
       <c r="L27" t="inlineStr"/>
@@ -1779,16 +1779,16 @@
         <v>120.48</v>
       </c>
       <c r="G28" t="n">
-        <v>1488664.996080711</v>
+        <v>1414360.012903227</v>
       </c>
       <c r="H28" t="n">
         <v>23715557.01062761</v>
       </c>
       <c r="I28" t="n">
-        <v>25204222.00670832</v>
+        <v>25129917.02353084</v>
       </c>
       <c r="J28" t="n">
-        <v>25204222.00670832</v>
+        <v>25129917.02353084</v>
       </c>
       <c r="K28" t="inlineStr"/>
       <c r="L28" t="inlineStr"/>
@@ -1810,16 +1810,16 @@
         <v>120.48</v>
       </c>
       <c r="G29" t="n">
-        <v>1655928.939685931</v>
+        <v>1414360.012903227</v>
       </c>
       <c r="H29" t="n">
         <v>24660958.77724204</v>
       </c>
       <c r="I29" t="n">
-        <v>26316887.71692798</v>
+        <v>26075318.79014527</v>
       </c>
       <c r="J29" t="n">
-        <v>26316887.71692798</v>
+        <v>26075318.79014527</v>
       </c>
       <c r="K29" t="inlineStr"/>
       <c r="L29" t="inlineStr"/>
@@ -4904,17 +4904,17 @@
         </is>
       </c>
       <c r="D107" t="n">
-        <v>9198978.795016408</v>
+        <v>0</v>
       </c>
       <c r="E107" t="n">
-        <v>7616182.132026732</v>
+        <v>0</v>
       </c>
       <c r="F107" t="n">
-        <v>10139377.46981212</v>
+        <v>0</v>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>첨예형</t>
+          <t>평탄형</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
@@ -4923,7 +4923,7 @@
         </is>
       </c>
       <c r="I107" t="n">
-        <v>24.8851109971759</v>
+        <v>0</v>
       </c>
     </row>
     <row r="108">
@@ -4962,13 +4962,13 @@
         </is>
       </c>
       <c r="D109" t="n">
-        <v>87554246.91252422</v>
+        <v>78167700.90515041</v>
       </c>
       <c r="E109" t="n">
-        <v>85681918.82675982</v>
+        <v>77880238.50656176</v>
       </c>
       <c r="F109" t="n">
-        <v>88489082.37075377</v>
+        <v>78167700.90515041</v>
       </c>
       <c r="G109" t="inlineStr">
         <is>
@@ -4977,11 +4977,11 @@
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>평탄형</t>
+          <t>기준</t>
         </is>
       </c>
       <c r="I109" t="n">
-        <v>3.17232755588133</v>
+        <v>0.3677508680183232</v>
       </c>
     </row>
     <row r="110">
@@ -4991,13 +4991,13 @@
         </is>
       </c>
       <c r="D110" t="n">
-        <v>87554246.91252422</v>
+        <v>78167700.90515041</v>
       </c>
       <c r="E110" t="n">
-        <v>85681918.82675982</v>
+        <v>77880238.50656176</v>
       </c>
       <c r="F110" t="n">
-        <v>88489082.37075377</v>
+        <v>78167700.90515041</v>
       </c>
       <c r="G110" t="inlineStr">
         <is>
@@ -5006,11 +5006,11 @@
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>평탄형</t>
+          <t>기준</t>
         </is>
       </c>
       <c r="I110" t="n">
-        <v>3.17232755588133</v>
+        <v>0.3677508680183232</v>
       </c>
     </row>
     <row r="111">
@@ -5020,13 +5020,13 @@
         </is>
       </c>
       <c r="D111" t="n">
-        <v>2732.308927852665</v>
+        <v>3603.8112</v>
       </c>
       <c r="E111" t="n">
-        <v>2724.427034790482</v>
+        <v>3603.8112</v>
       </c>
       <c r="F111" t="n">
-        <v>2745.502940153536</v>
+        <v>3603.8112</v>
       </c>
       <c r="G111" t="inlineStr">
         <is>
@@ -5035,11 +5035,11 @@
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>첨예형</t>
+          <t>평탄형</t>
         </is>
       </c>
       <c r="I111" t="n">
-        <v>0.767651895571288</v>
+        <v>0</v>
       </c>
     </row>
     <row r="112">
@@ -5102,17 +5102,17 @@
         </is>
       </c>
       <c r="D114" t="n">
-        <v>11238788.15785098</v>
+        <v>0</v>
       </c>
       <c r="E114" t="n">
-        <v>8120104.714053392</v>
+        <v>0</v>
       </c>
       <c r="F114" t="n">
-        <v>13105020.84234583</v>
+        <v>0</v>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>첨예형</t>
+          <t>평탄형</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
@@ -5121,7 +5121,7 @@
         </is>
       </c>
       <c r="I114" t="n">
-        <v>38.03821594991167</v>
+        <v>0</v>
       </c>
     </row>
     <row r="115">
@@ -5160,13 +5160,13 @@
         </is>
       </c>
       <c r="D116" t="n">
-        <v>167835324.5902858</v>
+        <v>156170236.5299845</v>
       </c>
       <c r="E116" t="n">
-        <v>164102472.5923471</v>
+        <v>155568191.3024335</v>
       </c>
       <c r="F116" t="n">
-        <v>169707067.1231384</v>
+        <v>156173110.5300727</v>
       </c>
       <c r="G116" t="inlineStr">
         <is>
@@ -5179,7 +5179,7 @@
         </is>
       </c>
       <c r="I116" t="n">
-        <v>3.302510983072156</v>
+        <v>0.3873389123044425</v>
       </c>
     </row>
     <row r="117">
@@ -5189,13 +5189,13 @@
         </is>
       </c>
       <c r="D117" t="n">
-        <v>167835324.5902858</v>
+        <v>156170236.5299845</v>
       </c>
       <c r="E117" t="n">
-        <v>164102472.5923471</v>
+        <v>155568191.3024335</v>
       </c>
       <c r="F117" t="n">
-        <v>169707067.1231384</v>
+        <v>156173110.5300727</v>
       </c>
       <c r="G117" t="inlineStr">
         <is>
@@ -5208,7 +5208,7 @@
         </is>
       </c>
       <c r="I117" t="n">
-        <v>3.302510983072156</v>
+        <v>0.3873389123044425</v>
       </c>
     </row>
     <row r="118">
@@ -5218,13 +5218,13 @@
         </is>
       </c>
       <c r="D118" t="n">
-        <v>2715.53785570533</v>
+        <v>3603.8112</v>
       </c>
       <c r="E118" t="n">
-        <v>2708.288549813411</v>
+        <v>3603.8112</v>
       </c>
       <c r="F118" t="n">
-        <v>2741.925880307072</v>
+        <v>3603.8112</v>
       </c>
       <c r="G118" t="inlineStr">
         <is>
@@ -5233,11 +5233,11 @@
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>첨예형</t>
+          <t>평탄형</t>
         </is>
       </c>
       <c r="I118" t="n">
-        <v>1.226777526527957</v>
+        <v>0</v>
       </c>
     </row>
     <row r="119">
@@ -5300,17 +5300,17 @@
         </is>
       </c>
       <c r="D121" t="n">
-        <v>14666364.50237396</v>
+        <v>0</v>
       </c>
       <c r="E121" t="n">
-        <v>9095591.485271841</v>
+        <v>0</v>
       </c>
       <c r="F121" t="n">
-        <v>18468749.66302106</v>
+        <v>0</v>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>첨예형</t>
+          <t>평탄형</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
@@ -5319,7 +5319,7 @@
         </is>
       </c>
       <c r="I121" t="n">
-        <v>50.75144960417416</v>
+        <v>0</v>
       </c>
     </row>
     <row r="122">
@@ -5358,13 +5358,13 @@
         </is>
       </c>
       <c r="D123" t="n">
-        <v>320373660.1922641</v>
+        <v>304639337.9363775</v>
       </c>
       <c r="E123" t="n">
-        <v>311615159.9630437</v>
+        <v>301520324.6918135</v>
       </c>
       <c r="F123" t="n">
-        <v>325559171.9981222</v>
+        <v>305988538.4193945</v>
       </c>
       <c r="G123" t="inlineStr">
         <is>
@@ -5377,7 +5377,7 @@
         </is>
       </c>
       <c r="I123" t="n">
-        <v>4.28309604963578</v>
+        <v>1.460255260102845</v>
       </c>
     </row>
     <row r="124">
@@ -5387,13 +5387,13 @@
         </is>
       </c>
       <c r="D124" t="n">
-        <v>320373660.1922641</v>
+        <v>304639337.9363775</v>
       </c>
       <c r="E124" t="n">
-        <v>311615159.9630437</v>
+        <v>301520324.6918135</v>
       </c>
       <c r="F124" t="n">
-        <v>325559171.9981222</v>
+        <v>305988538.4193945</v>
       </c>
       <c r="G124" t="inlineStr">
         <is>
@@ -5406,7 +5406,7 @@
         </is>
       </c>
       <c r="I124" t="n">
-        <v>4.28309604963578</v>
+        <v>1.460255260102845</v>
       </c>
     </row>
     <row r="125">
@@ -5416,13 +5416,13 @@
         </is>
       </c>
       <c r="D125" t="n">
-        <v>2701.871477154071</v>
+        <v>3603.8112</v>
       </c>
       <c r="E125" t="n">
-        <v>2690.857099626821</v>
+        <v>3603.8112</v>
       </c>
       <c r="F125" t="n">
-        <v>2734.771760614143</v>
+        <v>3603.8112</v>
       </c>
       <c r="G125" t="inlineStr">
         <is>
@@ -5431,11 +5431,11 @@
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>첨예형</t>
+          <t>평탄형</t>
         </is>
       </c>
       <c r="I125" t="n">
-        <v>1.60578888592372</v>
+        <v>0</v>
       </c>
     </row>
     <row r="126">
@@ -5503,13 +5503,13 @@
         </is>
       </c>
       <c r="D128" t="n">
-        <v>1381815.952363797</v>
+        <v>1360265.698040357</v>
       </c>
       <c r="E128" t="n">
-        <v>1006429.095233478</v>
+        <v>1006344.140394768</v>
       </c>
       <c r="F128" t="n">
-        <v>1589720.920636741</v>
+        <v>1414360.012903227</v>
       </c>
       <c r="G128" t="inlineStr">
         <is>
@@ -5522,7 +5522,7 @@
         </is>
       </c>
       <c r="I128" t="n">
-        <v>36.69146060993108</v>
+        <v>28.8480916305696</v>
       </c>
     </row>
     <row r="129">
@@ -5561,13 +5561,13 @@
         </is>
       </c>
       <c r="D130" t="n">
-        <v>22562082.16532806</v>
+        <v>22539261.19819576</v>
       </c>
       <c r="E130" t="n">
-        <v>20165934.02647321</v>
+        <v>20165845.00017712</v>
       </c>
       <c r="F130" t="n">
-        <v>24277784.97374577</v>
+        <v>24091200.96791732</v>
       </c>
       <c r="G130" t="inlineStr">
         <is>
@@ -5580,7 +5580,7 @@
         </is>
       </c>
       <c r="I130" t="n">
-        <v>16.93668080394961</v>
+        <v>16.29373302297241</v>
       </c>
     </row>
     <row r="131">
@@ -5590,13 +5590,13 @@
         </is>
       </c>
       <c r="D131" t="n">
-        <v>22562082.16532807</v>
+        <v>22539261.19819577</v>
       </c>
       <c r="E131" t="n">
-        <v>20165934.02647321</v>
+        <v>20165845.00017712</v>
       </c>
       <c r="F131" t="n">
-        <v>24277784.97374577</v>
+        <v>24091200.96791731</v>
       </c>
       <c r="G131" t="inlineStr">
         <is>
@@ -5609,7 +5609,7 @@
         </is>
       </c>
       <c r="I131" t="n">
-        <v>16.93668080394962</v>
+        <v>16.2937330229724</v>
       </c>
     </row>
     <row r="132">
@@ -5701,13 +5701,13 @@
         </is>
       </c>
       <c r="D135" t="n">
-        <v>1488664.996080711</v>
+        <v>1414360.012903227</v>
       </c>
       <c r="E135" t="n">
-        <v>1043277.277419355</v>
+        <v>1043192.322580645</v>
       </c>
       <c r="F135" t="n">
-        <v>1771658.825806452</v>
+        <v>1414360.012903227</v>
       </c>
       <c r="G135" t="inlineStr">
         <is>
@@ -5720,7 +5720,7 @@
         </is>
       </c>
       <c r="I135" t="n">
-        <v>41.11296925668185</v>
+        <v>26.24280147461845</v>
       </c>
     </row>
     <row r="136">
@@ -5759,13 +5759,13 @@
         </is>
       </c>
       <c r="D137" t="n">
-        <v>24502814.55603168</v>
+        <v>24423754.05393084</v>
       </c>
       <c r="E137" t="n">
-        <v>21582041.61871959</v>
+        <v>21581951.87274331</v>
       </c>
       <c r="F137" t="n">
-        <v>26325870.31366242</v>
+        <v>25945704.37673339</v>
       </c>
       <c r="G137" t="inlineStr">
         <is>
@@ -5778,7 +5778,7 @@
         </is>
       </c>
       <c r="I137" t="n">
-        <v>18.01964622032234</v>
+        <v>16.8187860334339</v>
       </c>
     </row>
     <row r="138">
@@ -5788,13 +5788,13 @@
         </is>
       </c>
       <c r="D138" t="n">
-        <v>24502814.55603169</v>
+        <v>24423754.05393084</v>
       </c>
       <c r="E138" t="n">
-        <v>21582041.61871959</v>
+        <v>21581951.87274331</v>
       </c>
       <c r="F138" t="n">
-        <v>26325870.31366242</v>
+        <v>25945704.37673339</v>
       </c>
       <c r="G138" t="inlineStr">
         <is>
@@ -5807,7 +5807,7 @@
         </is>
       </c>
       <c r="I138" t="n">
-        <v>18.01964622032234</v>
+        <v>16.8187860334339</v>
       </c>
     </row>
     <row r="139">
@@ -5899,13 +5899,13 @@
         </is>
       </c>
       <c r="D142" t="n">
-        <v>1655928.939685931</v>
+        <v>1414360.012903227</v>
       </c>
       <c r="E142" t="n">
-        <v>1043277.277419355</v>
+        <v>1043192.322580645</v>
       </c>
       <c r="F142" t="n">
-        <v>1771658.825806452</v>
+        <v>1414360.012903227</v>
       </c>
       <c r="G142" t="inlineStr">
         <is>
@@ -5918,7 +5918,7 @@
         </is>
       </c>
       <c r="I142" t="n">
-        <v>41.11296925668185</v>
+        <v>26.24280147461845</v>
       </c>
     </row>
     <row r="143">
@@ -5957,13 +5957,13 @@
         </is>
       </c>
       <c r="D144" t="n">
-        <v>25626185.15864207</v>
+        <v>25369155.82054527</v>
       </c>
       <c r="E144" t="n">
-        <v>22319085.09248485</v>
+        <v>22318994.92381698</v>
       </c>
       <c r="F144" t="n">
-        <v>26964477.82642099</v>
+        <v>26584311.88949196</v>
       </c>
       <c r="G144" t="inlineStr">
         <is>
@@ -5976,7 +5976,7 @@
         </is>
       </c>
       <c r="I144" t="n">
-        <v>17.22782382006443</v>
+        <v>16.04448888278708</v>
       </c>
     </row>
     <row r="145">
@@ -5986,13 +5986,13 @@
         </is>
       </c>
       <c r="D145" t="n">
-        <v>25626185.15864207</v>
+        <v>25369155.82054527</v>
       </c>
       <c r="E145" t="n">
-        <v>22319085.09248485</v>
+        <v>22318994.92381698</v>
       </c>
       <c r="F145" t="n">
-        <v>26964477.82642099</v>
+        <v>26584311.88949196</v>
       </c>
       <c r="G145" t="inlineStr">
         <is>
@@ -6005,7 +6005,7 @@
         </is>
       </c>
       <c r="I145" t="n">
-        <v>17.22782382006443</v>
+        <v>16.04448888278708</v>
       </c>
     </row>
     <row r="146">
@@ -6435,7 +6435,7 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>2762121670.457</v>
+        <v>2834769161.725</v>
       </c>
       <c r="D17" t="n">
         <v>0</v>
@@ -6451,10 +6451,10 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>2676057397.382</v>
+        <v>2759773065.99</v>
       </c>
       <c r="D18" t="n">
-        <v>86064273.07500029</v>
+        <v>74996095.73500013</v>
       </c>
       <c r="E18" t="b">
         <v>0</v>
@@ -6467,10 +6467,10 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>2682476659.66</v>
+        <v>2781184677.574</v>
       </c>
       <c r="D19" t="n">
-        <v>79645010.79699993</v>
+        <v>53584484.1510005</v>
       </c>
       <c r="E19" t="b">
         <v>0</v>
@@ -7170,10 +7170,10 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>86064273.07500029</v>
+        <v>74996095.73500013</v>
       </c>
       <c r="D27" t="n">
-        <v>86064273.07500029</v>
+        <v>74996095.73500013</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
@@ -7214,10 +7214,10 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>2395867.111000061</v>
+        <v>3122342.02368021</v>
       </c>
       <c r="D29" t="n">
-        <v>2395867.111000061</v>
+        <v>3122342.02368021</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
@@ -8690,7 +8690,7 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>증분 9,198,979 → 2,039,809 → 3,427,576</t>
+          <t>증분 0 → 0 → 0</t>
         </is>
       </c>
     </row>
@@ -8707,7 +8707,7 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>2,801.0 → 2,732.3 → 2,715.5 → 2,701.9</t>
+          <t>3,603.8 → 3,603.8 → 3,603.8 → 3,603.8</t>
         </is>
       </c>
     </row>
@@ -8775,7 +8775,7 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>86,064,273 원 · I → II</t>
+          <t>74,996,096 원 · I → II</t>
         </is>
       </c>
     </row>
@@ -8792,7 +8792,7 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>2,395,867 원 (기본요금 239,586,711 의 1.00%)</t>
+          <t>3,122,342 원 (기본요금 312,234,202 의 1.00%)</t>
         </is>
       </c>
     </row>
@@ -8933,7 +8933,7 @@
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>증분 1,381,816 → 106,849 → 167,264</t>
+          <t>증분 1,360,266 → 54,094 → 0</t>
         </is>
       </c>
     </row>
@@ -9193,14 +9193,14 @@
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>관측 10,920.6 kW vs 요금적용 2,801.0 kW (74.4% 낮다)</t>
+          <t>관측 10,920.6 kW vs 요금적용 3,603.8 kW (67.0% 낮다)</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="B104" t="inlineStr">
         <is>
-          <t>C6 야간 피크형의 PV 기여가 오히려 크다 (저감률)</t>
+          <t>C6 야간 피크형: 하한이 요금적용전력을 붙들어 PV 가 한 칸도 못 내린다</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
@@ -9210,7 +9210,7 @@
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>저감률 C6 3.05% vs C1 1.80% — 대상 슬롯이 주간뿐이라 PV 가 그대로 듣는다</t>
+          <t>C6 저감 0.00 kW vs C1 95.44 kW — 경부하 최대라 대상 수요가 하한 3,603.8 kW 아래에 있다</t>
         </is>
       </c>
     </row>
@@ -9287,7 +9287,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>8.1 초</t>
+          <t>7.9 초</t>
         </is>
       </c>
     </row>
@@ -9299,7 +9299,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>4.8 초</t>
+          <t>4.7 초</t>
         </is>
       </c>
     </row>
@@ -9311,7 +9311,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>8.4 초</t>
+          <t>8.2 초</t>
         </is>
       </c>
     </row>
@@ -9323,7 +9323,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>8.9 초</t>
+          <t>8.8 초</t>
         </is>
       </c>
     </row>
@@ -9335,7 +9335,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>5.7 초</t>
+          <t>5.6 초</t>
         </is>
       </c>
     </row>
@@ -9347,7 +9347,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>11.3 초</t>
+          <t>10.7 초</t>
         </is>
       </c>
     </row>
@@ -9359,7 +9359,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>58.3 초</t>
+          <t>56.9 초</t>
         </is>
       </c>
     </row>

--- a/output/casestudy_20260904.xlsx
+++ b/output/casestudy_20260904.xlsx
@@ -544,7 +544,7 @@
         </is>
       </c>
       <c r="N2" t="n">
-        <v>8.009656800000812</v>
+        <v>8.485695799998211</v>
       </c>
     </row>
     <row r="3">
@@ -596,7 +596,7 @@
         </is>
       </c>
       <c r="N3" t="n">
-        <v>7.90053959999932</v>
+        <v>8.130702999998903</v>
       </c>
     </row>
     <row r="4">
@@ -648,7 +648,7 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>4.712594500000705</v>
+        <v>4.843418000000383</v>
       </c>
     </row>
     <row r="5">
@@ -700,7 +700,7 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>8.214937499997177</v>
+        <v>8.335211300000083</v>
       </c>
     </row>
     <row r="6">
@@ -752,7 +752,7 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>8.76685709999947</v>
+        <v>8.994122899999638</v>
       </c>
     </row>
     <row r="7">
@@ -804,7 +804,7 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>5.599225300000398</v>
+        <v>5.734416200000851</v>
       </c>
     </row>
     <row r="8">
@@ -856,7 +856,7 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>10.74190250000174</v>
+        <v>10.7012001999974</v>
       </c>
     </row>
   </sheetData>
@@ -9275,7 +9275,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>8.0 초</t>
+          <t>8.5 초</t>
         </is>
       </c>
     </row>
@@ -9287,7 +9287,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>7.9 초</t>
+          <t>8.1 초</t>
         </is>
       </c>
     </row>
@@ -9299,7 +9299,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>4.7 초</t>
+          <t>4.8 초</t>
         </is>
       </c>
     </row>
@@ -9311,7 +9311,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>8.2 초</t>
+          <t>8.3 초</t>
         </is>
       </c>
     </row>
@@ -9323,7 +9323,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>8.8 초</t>
+          <t>9.0 초</t>
         </is>
       </c>
     </row>
@@ -9335,7 +9335,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>5.6 초</t>
+          <t>5.7 초</t>
         </is>
       </c>
     </row>
@@ -9359,7 +9359,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>56.9 초</t>
+          <t>58.2 초</t>
         </is>
       </c>
     </row>

--- a/output/casestudy_20260904.xlsx
+++ b/output/casestudy_20260904.xlsx
@@ -544,7 +544,7 @@
         </is>
       </c>
       <c r="N2" t="n">
-        <v>8.485695799998211</v>
+        <v>9.600171999998565</v>
       </c>
     </row>
     <row r="3">
@@ -596,7 +596,7 @@
         </is>
       </c>
       <c r="N3" t="n">
-        <v>8.130702999998903</v>
+        <v>8.678765199998452</v>
       </c>
     </row>
     <row r="4">
@@ -648,7 +648,7 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>4.843418000000383</v>
+        <v>4.908417499998905</v>
       </c>
     </row>
     <row r="5">
@@ -700,7 +700,7 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>8.335211300000083</v>
+        <v>8.421271300001536</v>
       </c>
     </row>
     <row r="6">
@@ -752,7 +752,7 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>8.994122899999638</v>
+        <v>9.223426199998357</v>
       </c>
     </row>
     <row r="7">
@@ -804,7 +804,7 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>5.734416200000851</v>
+        <v>5.887896699998237</v>
       </c>
     </row>
     <row r="8">
@@ -856,7 +856,7 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>10.7012001999974</v>
+        <v>11.9810409999991</v>
       </c>
     </row>
   </sheetData>
@@ -9275,7 +9275,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>8.5 초</t>
+          <t>9.6 초</t>
         </is>
       </c>
     </row>
@@ -9287,7 +9287,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>8.1 초</t>
+          <t>8.7 초</t>
         </is>
       </c>
     </row>
@@ -9299,7 +9299,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>4.8 초</t>
+          <t>4.9 초</t>
         </is>
       </c>
     </row>
@@ -9311,7 +9311,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>8.3 초</t>
+          <t>8.4 초</t>
         </is>
       </c>
     </row>
@@ -9323,7 +9323,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>9.0 초</t>
+          <t>9.2 초</t>
         </is>
       </c>
     </row>
@@ -9335,7 +9335,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>5.7 초</t>
+          <t>5.9 초</t>
         </is>
       </c>
     </row>
@@ -9347,7 +9347,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>10.7 초</t>
+          <t>12.0 초</t>
         </is>
       </c>
     </row>
@@ -9359,7 +9359,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>58.2 초</t>
+          <t>61.8 초</t>
         </is>
       </c>
     </row>

--- a/output/casestudy_20260904.xlsx
+++ b/output/casestudy_20260904.xlsx
@@ -544,7 +544,7 @@
         </is>
       </c>
       <c r="N2" t="n">
-        <v>9.600171999998565</v>
+        <v>9.971815500000957</v>
       </c>
     </row>
     <row r="3">
@@ -596,7 +596,7 @@
         </is>
       </c>
       <c r="N3" t="n">
-        <v>8.678765199998452</v>
+        <v>11.50575519999984</v>
       </c>
     </row>
     <row r="4">
@@ -648,7 +648,7 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>4.908417499998905</v>
+        <v>6.833812500000931</v>
       </c>
     </row>
     <row r="5">
@@ -700,7 +700,7 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>8.421271300001536</v>
+        <v>11.28747020000083</v>
       </c>
     </row>
     <row r="6">
@@ -752,7 +752,7 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>9.223426199998357</v>
+        <v>13.00167879999935</v>
       </c>
     </row>
     <row r="7">
@@ -804,7 +804,7 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>5.887896699998237</v>
+        <v>8.0990426999997</v>
       </c>
     </row>
     <row r="8">
@@ -856,7 +856,7 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>11.9810409999991</v>
+        <v>14.27413220000017</v>
       </c>
     </row>
   </sheetData>
@@ -9275,7 +9275,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>9.6 초</t>
+          <t>10.0 초</t>
         </is>
       </c>
     </row>
@@ -9287,7 +9287,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>8.7 초</t>
+          <t>11.5 초</t>
         </is>
       </c>
     </row>
@@ -9299,7 +9299,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>4.9 초</t>
+          <t>6.8 초</t>
         </is>
       </c>
     </row>
@@ -9311,7 +9311,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>8.4 초</t>
+          <t>11.3 초</t>
         </is>
       </c>
     </row>
@@ -9323,7 +9323,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>9.2 초</t>
+          <t>13.0 초</t>
         </is>
       </c>
     </row>
@@ -9335,7 +9335,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>5.9 초</t>
+          <t>8.1 초</t>
         </is>
       </c>
     </row>
@@ -9347,7 +9347,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>12.0 초</t>
+          <t>14.3 초</t>
         </is>
       </c>
     </row>
@@ -9359,7 +9359,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>61.8 초</t>
+          <t>78.9 초</t>
         </is>
       </c>
     </row>

--- a/output/casestudy_20260904.xlsx
+++ b/output/casestudy_20260904.xlsx
@@ -544,7 +544,7 @@
         </is>
       </c>
       <c r="N2" t="n">
-        <v>9.971815500000957</v>
+        <v>24.96197000006214</v>
       </c>
     </row>
     <row r="3">
@@ -596,7 +596,7 @@
         </is>
       </c>
       <c r="N3" t="n">
-        <v>11.50575519999984</v>
+        <v>24.71146219992079</v>
       </c>
     </row>
     <row r="4">
@@ -648,7 +648,7 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>6.833812500000931</v>
+        <v>16.12875450006686</v>
       </c>
     </row>
     <row r="5">
@@ -700,7 +700,7 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>11.28747020000083</v>
+        <v>25.42400019988418</v>
       </c>
     </row>
     <row r="6">
@@ -752,7 +752,7 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>13.00167879999935</v>
+        <v>26.2417592999991</v>
       </c>
     </row>
     <row r="7">
@@ -804,7 +804,7 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>8.0990426999997</v>
+        <v>20.21679410012439</v>
       </c>
     </row>
     <row r="8">
@@ -856,7 +856,7 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>14.27413220000017</v>
+        <v>34.05034240009263</v>
       </c>
     </row>
   </sheetData>
@@ -1909,13 +1909,13 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>12701893.61480463</v>
+        <v>-54354034.8372333</v>
       </c>
       <c r="E2" t="n">
-        <v>10889509.67217773</v>
+        <v>-56442543.75726879</v>
       </c>
       <c r="F2" t="n">
-        <v>12701893.61480463</v>
+        <v>-54354034.8372333</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -1928,7 +1928,7 @@
         </is>
       </c>
       <c r="I2" t="n">
-        <v>14.26861220530519</v>
+        <v>3.700238828740809</v>
       </c>
     </row>
     <row r="3">
@@ -1938,13 +1938,13 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>78883246.71788597</v>
+        <v>198235738.4790244</v>
       </c>
       <c r="E3" t="n">
-        <v>78601846.13266468</v>
+        <v>197954047.4566307</v>
       </c>
       <c r="F3" t="n">
-        <v>78883246.71788597</v>
+        <v>198235738.4790244</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -1957,7 +1957,7 @@
         </is>
       </c>
       <c r="I3" t="n">
-        <v>0.3567304807162379</v>
+        <v>0.1420990102768526</v>
       </c>
     </row>
     <row r="4">
@@ -1967,13 +1967,13 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>91089226.44079876</v>
+        <v>143310235.0018272</v>
       </c>
       <c r="E4" t="n">
-        <v>88989374.69005966</v>
+        <v>140933043.4673686</v>
       </c>
       <c r="F4" t="n">
-        <v>91089226.44079876</v>
+        <v>143310235.0018272</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -1986,7 +1986,7 @@
         </is>
       </c>
       <c r="I4" t="n">
-        <v>2.30526905627401</v>
+        <v>1.658773034897561</v>
       </c>
     </row>
     <row r="5">
@@ -1996,13 +1996,13 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>91089226.44079876</v>
+        <v>143310235.0018272</v>
       </c>
       <c r="E5" t="n">
-        <v>88989374.69005966</v>
+        <v>140933043.4673686</v>
       </c>
       <c r="F5" t="n">
-        <v>91089226.44079876</v>
+        <v>143310235.0018272</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -2015,7 +2015,7 @@
         </is>
       </c>
       <c r="I5" t="n">
-        <v>2.30526905627401</v>
+        <v>1.658773034897561</v>
       </c>
     </row>
     <row r="6">
@@ -2107,13 +2107,13 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>17959850.53636867</v>
+        <v>-48295004.14645588</v>
       </c>
       <c r="E9" t="n">
-        <v>14329712.14435565</v>
+        <v>-52478210.71453762</v>
       </c>
       <c r="F9" t="n">
-        <v>19802599.69234592</v>
+        <v>-46171503.7340281</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -2126,7 +2126,7 @@
         </is>
       </c>
       <c r="I9" t="n">
-        <v>27.63721750182951</v>
+        <v>12.01776298131755</v>
       </c>
     </row>
     <row r="10">
@@ -2136,13 +2136,13 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>157766493.4357724</v>
+        <v>273905077.3980494</v>
       </c>
       <c r="E10" t="n">
-        <v>157203692.2653284</v>
+        <v>273341695.35326</v>
       </c>
       <c r="F10" t="n">
-        <v>157766493.4357724</v>
+        <v>273905077.3980494</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -2155,7 +2155,7 @@
         </is>
       </c>
       <c r="I10" t="n">
-        <v>0.3567304807171435</v>
+        <v>0.2056851410500091</v>
       </c>
     </row>
     <row r="11">
@@ -2165,13 +2165,13 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>174695374.9795818</v>
+        <v>224422031.4208326</v>
       </c>
       <c r="E11" t="n">
-        <v>170484995.4955649</v>
+        <v>219655345.8346405</v>
       </c>
       <c r="F11" t="n">
-        <v>176526740.9757071</v>
+        <v>226537598.7361746</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -2184,7 +2184,7 @@
         </is>
       </c>
       <c r="I11" t="n">
-        <v>3.422566715245459</v>
+        <v>3.038017944892735</v>
       </c>
     </row>
     <row r="12">
@@ -2194,13 +2194,13 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>174695374.9795818</v>
+        <v>224422031.4208326</v>
       </c>
       <c r="E12" t="n">
-        <v>170484995.4955649</v>
+        <v>219655345.8346405</v>
       </c>
       <c r="F12" t="n">
-        <v>176526740.9757071</v>
+        <v>226537598.7361746</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -2213,7 +2213,7 @@
         </is>
       </c>
       <c r="I12" t="n">
-        <v>3.422566715245459</v>
+        <v>3.038017944892735</v>
       </c>
     </row>
     <row r="13">
@@ -2305,13 +2305,13 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>21857047.88703465</v>
+        <v>-43804050.96674138</v>
       </c>
       <c r="E16" t="n">
-        <v>15930141.24101007</v>
+        <v>-50633948.93002719</v>
       </c>
       <c r="F16" t="n">
-        <v>25626701.78469169</v>
+        <v>-39460073.06805611</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
@@ -2324,7 +2324,7 @@
         </is>
       </c>
       <c r="I16" t="n">
-        <v>37.8377234228165</v>
+        <v>22.06795262485383</v>
       </c>
     </row>
     <row r="17">
@@ -2334,13 +2334,13 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>315532986.8715444</v>
+        <v>425243755.2360973</v>
       </c>
       <c r="E17" t="n">
-        <v>314395380.2260122</v>
+        <v>424105698.3038983</v>
       </c>
       <c r="F17" t="n">
-        <v>315532986.8715444</v>
+        <v>425243755.2360973</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
@@ -2353,7 +2353,7 @@
         </is>
       </c>
       <c r="I17" t="n">
-        <v>0.3605349338626388</v>
+        <v>0.2676246078127936</v>
       </c>
     </row>
     <row r="18">
@@ -2363,13 +2363,13 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>335115969.2951603</v>
+        <v>378819174.5386577</v>
       </c>
       <c r="E18" t="n">
-        <v>327998630.7924576</v>
+        <v>370790346.2696633</v>
       </c>
       <c r="F18" t="n">
-        <v>338880327.16399</v>
+        <v>383167418.2127137</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
@@ -2382,7 +2382,7 @@
         </is>
       </c>
       <c r="I18" t="n">
-        <v>3.211073496829635</v>
+        <v>3.230199478020156</v>
       </c>
     </row>
     <row r="19">
@@ -2392,13 +2392,13 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>335115969.2951603</v>
+        <v>378819174.5386577</v>
       </c>
       <c r="E19" t="n">
-        <v>327998630.7924576</v>
+        <v>370790346.2696633</v>
       </c>
       <c r="F19" t="n">
-        <v>338880327.16399</v>
+        <v>383167418.2127137</v>
       </c>
       <c r="G19" t="inlineStr">
         <is>
@@ -2411,7 +2411,7 @@
         </is>
       </c>
       <c r="I19" t="n">
-        <v>3.211073496829635</v>
+        <v>3.230199478020156</v>
       </c>
     </row>
     <row r="20">
@@ -2508,13 +2508,13 @@
         </is>
       </c>
       <c r="D23" t="n">
-        <v>1250215.199999928</v>
+        <v>-67550428.80000013</v>
       </c>
       <c r="E23" t="n">
-        <v>1250215.199999928</v>
+        <v>-67550428.80000013</v>
       </c>
       <c r="F23" t="n">
-        <v>1250215.199999928</v>
+        <v>-67550428.80000013</v>
       </c>
       <c r="G23" t="inlineStr">
         <is>
@@ -2537,13 +2537,13 @@
         </is>
       </c>
       <c r="D24" t="n">
-        <v>78577461.91935921</v>
+        <v>197703038.6228766</v>
       </c>
       <c r="E24" t="n">
-        <v>78286775.6927371</v>
+        <v>197412263.7948275</v>
       </c>
       <c r="F24" t="n">
-        <v>78577461.91935921</v>
+        <v>197703038.6228766</v>
       </c>
       <c r="G24" t="inlineStr">
         <is>
@@ -2556,7 +2556,7 @@
         </is>
       </c>
       <c r="I24" t="n">
-        <v>0.3699358817677566</v>
+        <v>0.1470765599125884</v>
       </c>
     </row>
     <row r="25">
@@ -2566,13 +2566,13 @@
         </is>
       </c>
       <c r="D25" t="n">
-        <v>79319852.16566801</v>
+        <v>129567415.4164071</v>
       </c>
       <c r="E25" t="n">
-        <v>79025103.52082205</v>
+        <v>129271959.2421498</v>
       </c>
       <c r="F25" t="n">
-        <v>79319852.16566801</v>
+        <v>129567415.4164071</v>
       </c>
       <c r="G25" t="inlineStr">
         <is>
@@ -2585,7 +2585,7 @@
         </is>
       </c>
       <c r="I25" t="n">
-        <v>0.3715950506694697</v>
+        <v>0.228032776070846</v>
       </c>
     </row>
     <row r="26">
@@ -2595,13 +2595,13 @@
         </is>
       </c>
       <c r="D26" t="n">
-        <v>79319852.16566801</v>
+        <v>129567415.4164071</v>
       </c>
       <c r="E26" t="n">
-        <v>79025103.52082205</v>
+        <v>129271959.2421498</v>
       </c>
       <c r="F26" t="n">
-        <v>79319852.16566801</v>
+        <v>129567415.4164071</v>
       </c>
       <c r="G26" t="inlineStr">
         <is>
@@ -2614,7 +2614,7 @@
         </is>
       </c>
       <c r="I26" t="n">
-        <v>0.3715950506694697</v>
+        <v>0.228032776070846</v>
       </c>
     </row>
     <row r="27">
@@ -2706,13 +2706,13 @@
         </is>
       </c>
       <c r="D30" t="n">
-        <v>1250215.199999928</v>
+        <v>-67550428.80000013</v>
       </c>
       <c r="E30" t="n">
-        <v>1250215.199999928</v>
+        <v>-67550428.80000013</v>
       </c>
       <c r="F30" t="n">
-        <v>1250215.199999928</v>
+        <v>-67550428.80000013</v>
       </c>
       <c r="G30" t="inlineStr">
         <is>
@@ -2735,13 +2735,13 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>157154857.0227194</v>
+        <v>273077903.8697543</v>
       </c>
       <c r="E31" t="n">
-        <v>156573484.5694752</v>
+        <v>272496354.213655</v>
       </c>
       <c r="F31" t="n">
-        <v>157154857.0227194</v>
+        <v>273077903.8697543</v>
       </c>
       <c r="G31" t="inlineStr">
         <is>
@@ -2754,7 +2754,7 @@
         </is>
       </c>
       <c r="I31" t="n">
-        <v>0.3699360390497903</v>
+        <v>0.2129610810168999</v>
       </c>
     </row>
     <row r="32">
@@ -2764,13 +2764,13 @@
         </is>
       </c>
       <c r="D32" t="n">
-        <v>157336682.9712462</v>
+        <v>204296311.8325996</v>
       </c>
       <c r="E32" t="n">
-        <v>156746326.7116151</v>
+        <v>203704409.6461487</v>
       </c>
       <c r="F32" t="n">
-        <v>157336682.9712462</v>
+        <v>204296311.8325996</v>
       </c>
       <c r="G32" t="inlineStr">
         <is>
@@ -2783,7 +2783,7 @@
         </is>
       </c>
       <c r="I32" t="n">
-        <v>0.3752184477786699</v>
+        <v>0.2897272991085433</v>
       </c>
     </row>
     <row r="33">
@@ -2793,13 +2793,13 @@
         </is>
       </c>
       <c r="D33" t="n">
-        <v>157336682.9712462</v>
+        <v>204296311.8325996</v>
       </c>
       <c r="E33" t="n">
-        <v>156746326.7116151</v>
+        <v>203704409.6461487</v>
       </c>
       <c r="F33" t="n">
-        <v>157336682.9712462</v>
+        <v>204296311.8325996</v>
       </c>
       <c r="G33" t="inlineStr">
         <is>
@@ -2812,7 +2812,7 @@
         </is>
       </c>
       <c r="I33" t="n">
-        <v>0.3752184477786699</v>
+        <v>0.2897272991085433</v>
       </c>
     </row>
     <row r="34">
@@ -2904,13 +2904,13 @@
         </is>
       </c>
       <c r="D37" t="n">
-        <v>1250215.199999928</v>
+        <v>-67550428.80000013</v>
       </c>
       <c r="E37" t="n">
-        <v>1250215.199999928</v>
+        <v>-67550428.80000013</v>
       </c>
       <c r="F37" t="n">
-        <v>1250215.199999928</v>
+        <v>-67550428.80000013</v>
       </c>
       <c r="G37" t="inlineStr">
         <is>
@@ -2933,13 +2933,13 @@
         </is>
       </c>
       <c r="D38" t="n">
-        <v>314299480.3542247</v>
+        <v>423818070.0509415</v>
       </c>
       <c r="E38" t="n">
-        <v>313102844.4187264</v>
+        <v>422623088.3375292</v>
       </c>
       <c r="F38" t="n">
-        <v>314299480.3542247</v>
+        <v>423818070.0509415</v>
       </c>
       <c r="G38" t="inlineStr">
         <is>
@@ -2952,7 +2952,7 @@
         </is>
       </c>
       <c r="I38" t="n">
-        <v>0.3807311212063074</v>
+        <v>0.2819562915919683</v>
       </c>
     </row>
     <row r="39">
@@ -2962,13 +2962,13 @@
         </is>
       </c>
       <c r="D39" t="n">
-        <v>313172441.4176869</v>
+        <v>353528201.5811362</v>
       </c>
       <c r="E39" t="n">
-        <v>311954117.7694283</v>
+        <v>352308227.9327974</v>
       </c>
       <c r="F39" t="n">
-        <v>313175233.8550706</v>
+        <v>353537323.204761</v>
       </c>
       <c r="G39" t="inlineStr">
         <is>
@@ -2981,7 +2981,7 @@
         </is>
       </c>
       <c r="I39" t="n">
-        <v>0.3899146399959068</v>
+        <v>0.3476564400109268</v>
       </c>
     </row>
     <row r="40">
@@ -2991,13 +2991,13 @@
         </is>
       </c>
       <c r="D40" t="n">
-        <v>313172441.4176869</v>
+        <v>353528201.5811362</v>
       </c>
       <c r="E40" t="n">
-        <v>311954117.7694283</v>
+        <v>352308227.9327974</v>
       </c>
       <c r="F40" t="n">
-        <v>313175233.8550706</v>
+        <v>353537323.204761</v>
       </c>
       <c r="G40" t="inlineStr">
         <is>
@@ -3010,7 +3010,7 @@
         </is>
       </c>
       <c r="I40" t="n">
-        <v>0.3899146399959068</v>
+        <v>0.3476564400109268</v>
       </c>
     </row>
     <row r="41">
@@ -3107,13 +3107,13 @@
         </is>
       </c>
       <c r="D44" t="n">
-        <v>4260002.071758658</v>
+        <v>-88724162.93989575</v>
       </c>
       <c r="E44" t="n">
-        <v>2856997.28704375</v>
+        <v>-90630461.68477851</v>
       </c>
       <c r="F44" t="n">
-        <v>5207487.57249558</v>
+        <v>-87436789.98113811</v>
       </c>
       <c r="G44" t="inlineStr">
         <is>
@@ -3126,7 +3126,7 @@
         </is>
       </c>
       <c r="I44" t="n">
-        <v>45.13674305948283</v>
+        <v>3.523839164306919</v>
       </c>
     </row>
     <row r="45">
@@ -3136,13 +3136,13 @@
         </is>
       </c>
       <c r="D45" t="n">
-        <v>78883246.71788597</v>
+        <v>253182269.6127067</v>
       </c>
       <c r="E45" t="n">
-        <v>78601846.13266373</v>
+        <v>252977276.5257425</v>
       </c>
       <c r="F45" t="n">
-        <v>78883246.71788597</v>
+        <v>253182269.6127067</v>
       </c>
       <c r="G45" t="inlineStr">
         <is>
@@ -3155,7 +3155,7 @@
         </is>
       </c>
       <c r="I45" t="n">
-        <v>0.3567304807174468</v>
+        <v>0.08096660452475944</v>
       </c>
     </row>
     <row r="46">
@@ -3165,13 +3165,13 @@
         </is>
       </c>
       <c r="D46" t="n">
-        <v>82808665.0878582</v>
+        <v>164003499.1777244</v>
       </c>
       <c r="E46" t="n">
-        <v>81119710.90947247</v>
+        <v>161886026.7626529</v>
       </c>
       <c r="F46" t="n">
-        <v>83746710.66527748</v>
+        <v>165245788.2723513</v>
       </c>
       <c r="G46" t="inlineStr">
         <is>
@@ -3184,7 +3184,7 @@
         </is>
       </c>
       <c r="I46" t="n">
-        <v>3.136839327701745</v>
+        <v>2.033190403716052</v>
       </c>
     </row>
     <row r="47">
@@ -3194,13 +3194,13 @@
         </is>
       </c>
       <c r="D47" t="n">
-        <v>82808665.0878582</v>
+        <v>164003499.1777244</v>
       </c>
       <c r="E47" t="n">
-        <v>81119710.90947247</v>
+        <v>161886026.7626529</v>
       </c>
       <c r="F47" t="n">
-        <v>83746710.66527748</v>
+        <v>165245788.2723513</v>
       </c>
       <c r="G47" t="inlineStr">
         <is>
@@ -3213,7 +3213,7 @@
         </is>
       </c>
       <c r="I47" t="n">
-        <v>3.136839327701745</v>
+        <v>2.033190403716052</v>
       </c>
     </row>
     <row r="48">
@@ -3305,13 +3305,13 @@
         </is>
       </c>
       <c r="D51" t="n">
-        <v>5914690.769764483</v>
+        <v>-86475894.77820092</v>
       </c>
       <c r="E51" t="n">
-        <v>3227809.433008671</v>
+        <v>-90126629.66927767</v>
       </c>
       <c r="F51" t="n">
-        <v>7705960.109821439</v>
+        <v>-84042050.97959155</v>
       </c>
       <c r="G51" t="inlineStr">
         <is>
@@ -3324,7 +3324,7 @@
         </is>
       </c>
       <c r="I51" t="n">
-        <v>58.11281933714207</v>
+        <v>6.751144153524503</v>
       </c>
     </row>
     <row r="52">
@@ -3334,13 +3334,13 @@
         </is>
       </c>
       <c r="D52" t="n">
-        <v>157766493.4357719</v>
+        <v>327213343.368413</v>
       </c>
       <c r="E52" t="n">
-        <v>157203692.2653279</v>
+        <v>326803357.1944852</v>
       </c>
       <c r="F52" t="n">
-        <v>157766493.4357719</v>
+        <v>327213343.368413</v>
       </c>
       <c r="G52" t="inlineStr">
         <is>
@@ -3353,7 +3353,7 @@
         </is>
       </c>
       <c r="I52" t="n">
-        <v>0.3567304807171446</v>
+        <v>0.12529628825869</v>
       </c>
     </row>
     <row r="53">
@@ -3363,13 +3363,13 @@
         </is>
       </c>
       <c r="D53" t="n">
-        <v>162976496.4152608</v>
+        <v>239779971.1355581</v>
       </c>
       <c r="E53" t="n">
-        <v>159713326.8771558</v>
+        <v>235700924.8942127</v>
       </c>
       <c r="F53" t="n">
-        <v>164752351.2384591</v>
+        <v>242128355.6387472</v>
       </c>
       <c r="G53" t="inlineStr">
         <is>
@@ -3382,7 +3382,7 @@
         </is>
       </c>
       <c r="I53" t="n">
-        <v>3.058544733003507</v>
+        <v>2.654555154260473</v>
       </c>
     </row>
     <row r="54">
@@ -3392,13 +3392,13 @@
         </is>
       </c>
       <c r="D54" t="n">
-        <v>162976496.4152608</v>
+        <v>239779971.1355581</v>
       </c>
       <c r="E54" t="n">
-        <v>159713326.8771558</v>
+        <v>235700924.8942127</v>
       </c>
       <c r="F54" t="n">
-        <v>164752351.2384591</v>
+        <v>242128355.6387472</v>
       </c>
       <c r="G54" t="inlineStr">
         <is>
@@ -3411,7 +3411,7 @@
         </is>
       </c>
       <c r="I54" t="n">
-        <v>3.058544733003507</v>
+        <v>2.654555154260473</v>
       </c>
     </row>
     <row r="55">
@@ -3503,13 +3503,13 @@
         </is>
       </c>
       <c r="D58" t="n">
-        <v>8553308.208888471</v>
+        <v>-30283931.19141936</v>
       </c>
       <c r="E58" t="n">
-        <v>3545599.328757107</v>
+        <v>-36054587.40785885</v>
       </c>
       <c r="F58" t="n">
-        <v>9797105.50560087</v>
+        <v>-28850635.69160682</v>
       </c>
       <c r="G58" t="inlineStr">
         <is>
@@ -3522,7 +3522,7 @@
         </is>
       </c>
       <c r="I58" t="n">
-        <v>63.80972597743142</v>
+        <v>19.98067994721187</v>
       </c>
     </row>
     <row r="59">
@@ -3532,13 +3532,13 @@
         </is>
       </c>
       <c r="D59" t="n">
-        <v>315532986.8715444</v>
+        <v>425243754.8510966</v>
       </c>
       <c r="E59" t="n">
-        <v>314407384.5306559</v>
+        <v>424116990.7615199</v>
       </c>
       <c r="F59" t="n">
-        <v>315532986.8715444</v>
+        <v>425243754.8510966</v>
       </c>
       <c r="G59" t="inlineStr">
         <is>
@@ -3551,7 +3551,7 @@
         </is>
       </c>
       <c r="I59" t="n">
-        <v>0.3567304807172952</v>
+        <v>0.2649689917189422</v>
       </c>
     </row>
     <row r="60">
@@ -3561,13 +3561,13 @@
         </is>
       </c>
       <c r="D60" t="n">
-        <v>322508060.0090222</v>
+        <v>393141137.2615976</v>
       </c>
       <c r="E60" t="n">
-        <v>316328145.3441987</v>
+        <v>386190013.2641063</v>
       </c>
       <c r="F60" t="n">
-        <v>323724212.857944</v>
+        <v>394552945.2340436</v>
       </c>
       <c r="G60" t="inlineStr">
         <is>
@@ -3580,7 +3580,7 @@
         </is>
       </c>
       <c r="I60" t="n">
-        <v>2.28468159624218</v>
+        <v>2.11959689338437</v>
       </c>
     </row>
     <row r="61">
@@ -3590,13 +3590,13 @@
         </is>
       </c>
       <c r="D61" t="n">
-        <v>322508060.0090222</v>
+        <v>393141137.2615976</v>
       </c>
       <c r="E61" t="n">
-        <v>316328145.3441987</v>
+        <v>386190013.2641063</v>
       </c>
       <c r="F61" t="n">
-        <v>323724212.857944</v>
+        <v>394552945.2340436</v>
       </c>
       <c r="G61" t="inlineStr">
         <is>
@@ -3609,7 +3609,7 @@
         </is>
       </c>
       <c r="I61" t="n">
-        <v>2.28468159624218</v>
+        <v>2.11959689338437</v>
       </c>
     </row>
     <row r="62">
@@ -3706,13 +3706,13 @@
         </is>
       </c>
       <c r="D65" t="n">
-        <v>12701893.61480463</v>
+        <v>-54354034.8372333</v>
       </c>
       <c r="E65" t="n">
-        <v>10889509.67217773</v>
+        <v>-56442543.75726879</v>
       </c>
       <c r="F65" t="n">
-        <v>12701893.61480463</v>
+        <v>-54354034.8372333</v>
       </c>
       <c r="G65" t="inlineStr">
         <is>
@@ -3725,7 +3725,7 @@
         </is>
       </c>
       <c r="I65" t="n">
-        <v>14.26861220530519</v>
+        <v>3.700238828740809</v>
       </c>
     </row>
     <row r="66">
@@ -3735,13 +3735,13 @@
         </is>
       </c>
       <c r="D66" t="n">
-        <v>89087627.11786318</v>
+        <v>217067559.6463842</v>
       </c>
       <c r="E66" t="n">
-        <v>88742994.60184193</v>
+        <v>216730025.1961231</v>
       </c>
       <c r="F66" t="n">
-        <v>89169350.90986013</v>
+        <v>217143970.8550892</v>
       </c>
       <c r="G66" t="inlineStr">
         <is>
@@ -3754,7 +3754,7 @@
         </is>
       </c>
       <c r="I66" t="n">
-        <v>0.4781422132916548</v>
+        <v>0.1906318915215522</v>
       </c>
     </row>
     <row r="67">
@@ -3764,13 +3764,13 @@
         </is>
       </c>
       <c r="D67" t="n">
-        <v>101329735.4428229</v>
+        <v>162183689.1288862</v>
       </c>
       <c r="E67" t="n">
-        <v>99167106.6073904</v>
+        <v>159751178.3105502</v>
       </c>
       <c r="F67" t="n">
-        <v>101347227.0178547</v>
+        <v>162186082.0487895</v>
       </c>
       <c r="G67" t="inlineStr">
         <is>
@@ -3783,7 +3783,7 @@
         </is>
       </c>
       <c r="I67" t="n">
-        <v>2.151139675563306</v>
+        <v>1.501302520833329</v>
       </c>
     </row>
     <row r="68">
@@ -3793,13 +3793,13 @@
         </is>
       </c>
       <c r="D68" t="n">
-        <v>101329735.4428229</v>
+        <v>162183689.1288862</v>
       </c>
       <c r="E68" t="n">
-        <v>99167106.6073904</v>
+        <v>159751178.3105502</v>
       </c>
       <c r="F68" t="n">
-        <v>101347227.0178547</v>
+        <v>162186082.0487895</v>
       </c>
       <c r="G68" t="inlineStr">
         <is>
@@ -3812,7 +3812,7 @@
         </is>
       </c>
       <c r="I68" t="n">
-        <v>2.151139675563306</v>
+        <v>1.501302520833329</v>
       </c>
     </row>
     <row r="69">
@@ -3904,13 +3904,13 @@
         </is>
       </c>
       <c r="D72" t="n">
-        <v>17959850.53636867</v>
+        <v>-48295004.14645588</v>
       </c>
       <c r="E72" t="n">
-        <v>14329712.14435565</v>
+        <v>-52478210.71453762</v>
       </c>
       <c r="F72" t="n">
-        <v>19802599.69234592</v>
+        <v>-46171503.7340281</v>
       </c>
       <c r="G72" t="inlineStr">
         <is>
@@ -3923,7 +3923,7 @@
         </is>
       </c>
       <c r="I72" t="n">
-        <v>27.63721750182951</v>
+        <v>12.01776298131755</v>
       </c>
     </row>
     <row r="73">
@@ -3933,13 +3933,13 @@
         </is>
       </c>
       <c r="D73" t="n">
-        <v>178175254.2357264</v>
+        <v>303042324.7127686</v>
       </c>
       <c r="E73" t="n">
-        <v>177485989.2036839</v>
+        <v>302367255.8122468</v>
       </c>
       <c r="F73" t="n">
-        <v>178338701.8197207</v>
+        <v>303195147.1301785</v>
       </c>
       <c r="G73" t="inlineStr">
         <is>
@@ -3952,7 +3952,7 @@
         </is>
       </c>
       <c r="I73" t="n">
-        <v>0.4781422132919209</v>
+        <v>0.2730555966241084</v>
       </c>
     </row>
     <row r="74">
@@ -3962,13 +3962,13 @@
         </is>
       </c>
       <c r="D74" t="n">
-        <v>195182776.5672636</v>
+        <v>253649900.8067284</v>
       </c>
       <c r="E74" t="n">
-        <v>190847320.5621276</v>
+        <v>248773127.0729461</v>
       </c>
       <c r="F74" t="n">
-        <v>197206558.5548496</v>
+        <v>255946488.0770307</v>
       </c>
       <c r="G74" t="inlineStr">
         <is>
@@ -3981,7 +3981,7 @@
         </is>
       </c>
       <c r="I74" t="n">
-        <v>3.224658469435905</v>
+        <v>2.80267998907868</v>
       </c>
     </row>
     <row r="75">
@@ -3991,13 +3991,13 @@
         </is>
       </c>
       <c r="D75" t="n">
-        <v>195182776.5672636</v>
+        <v>253649900.8067284</v>
       </c>
       <c r="E75" t="n">
-        <v>190847320.5621276</v>
+        <v>248773127.0729461</v>
       </c>
       <c r="F75" t="n">
-        <v>197206558.5548496</v>
+        <v>255946488.0770307</v>
       </c>
       <c r="G75" t="inlineStr">
         <is>
@@ -4010,7 +4010,7 @@
         </is>
       </c>
       <c r="I75" t="n">
-        <v>3.224658469435905</v>
+        <v>2.80267998907868</v>
       </c>
     </row>
     <row r="76">
@@ -4102,13 +4102,13 @@
         </is>
       </c>
       <c r="D79" t="n">
-        <v>21857047.88703465</v>
+        <v>-43804050.96674138</v>
       </c>
       <c r="E79" t="n">
-        <v>15930141.24101007</v>
+        <v>-50633948.93002719</v>
       </c>
       <c r="F79" t="n">
-        <v>25626701.78469169</v>
+        <v>-39460073.06805611</v>
       </c>
       <c r="G79" t="inlineStr">
         <is>
@@ -4121,7 +4121,7 @@
         </is>
       </c>
       <c r="I79" t="n">
-        <v>37.8377234228165</v>
+        <v>22.06795262485383</v>
       </c>
     </row>
     <row r="80">
@@ -4131,13 +4131,13 @@
         </is>
       </c>
       <c r="D80" t="n">
-        <v>356350508.4714532</v>
+        <v>474991854.8455372</v>
       </c>
       <c r="E80" t="n">
-        <v>354971978.4073682</v>
+        <v>473641717.0444932</v>
       </c>
       <c r="F80" t="n">
-        <v>356677403.6394429</v>
+        <v>475297499.6803584</v>
       </c>
       <c r="G80" t="inlineStr">
         <is>
@@ -4150,7 +4150,7 @@
         </is>
       </c>
       <c r="I80" t="n">
-        <v>0.4781422132921863</v>
+        <v>0.3483676301640003</v>
       </c>
     </row>
     <row r="81">
@@ -4160,13 +4160,13 @@
         </is>
       </c>
       <c r="D81" t="n">
-        <v>376124065.2845831</v>
+        <v>428786883.4169002</v>
       </c>
       <c r="E81" t="n">
-        <v>368770372.4855566</v>
+        <v>420551239.5279455</v>
       </c>
       <c r="F81" t="n">
-        <v>380271226.7654672</v>
+        <v>433494829.5984359</v>
       </c>
       <c r="G81" t="inlineStr">
         <is>
@@ -4179,7 +4179,7 @@
         </is>
       </c>
       <c r="I81" t="n">
-        <v>3.024381933320381</v>
+        <v>2.985869539085516</v>
       </c>
     </row>
     <row r="82">
@@ -4189,13 +4189,13 @@
         </is>
       </c>
       <c r="D82" t="n">
-        <v>376124065.2845831</v>
+        <v>428786883.4169002</v>
       </c>
       <c r="E82" t="n">
-        <v>368770372.4855566</v>
+        <v>420551239.5279455</v>
       </c>
       <c r="F82" t="n">
-        <v>380271226.7654672</v>
+        <v>433494829.5984359</v>
       </c>
       <c r="G82" t="inlineStr">
         <is>
@@ -4208,7 +4208,7 @@
         </is>
       </c>
       <c r="I82" t="n">
-        <v>3.024381933320381</v>
+        <v>2.985869539085516</v>
       </c>
     </row>
     <row r="83">
@@ -4305,13 +4305,13 @@
         </is>
       </c>
       <c r="D86" t="n">
-        <v>4562905.771586657</v>
+        <v>-62078458.67872566</v>
       </c>
       <c r="E86" t="n">
-        <v>3360661.218680143</v>
+        <v>-63463870.68429112</v>
       </c>
       <c r="F86" t="n">
-        <v>5042317.021607995</v>
+        <v>-61526006.93354869</v>
       </c>
       <c r="G86" t="inlineStr">
         <is>
@@ -4324,7 +4324,7 @@
         </is>
       </c>
       <c r="I86" t="n">
-        <v>33.35085429419453</v>
+        <v>3.053491269674644</v>
       </c>
     </row>
     <row r="87">
@@ -4334,13 +4334,13 @@
         </is>
       </c>
       <c r="D87" t="n">
-        <v>78883246.71788645</v>
+        <v>191137183.9390244</v>
       </c>
       <c r="E87" t="n">
-        <v>78601846.13266468</v>
+        <v>190855492.9166307</v>
       </c>
       <c r="F87" t="n">
-        <v>78883246.71788645</v>
+        <v>191137183.9390244</v>
       </c>
       <c r="G87" t="inlineStr">
         <is>
@@ -4353,7 +4353,7 @@
         </is>
       </c>
       <c r="I87" t="n">
-        <v>0.3567304807168402</v>
+        <v>0.1473763590048324</v>
       </c>
     </row>
     <row r="88">
@@ -4363,13 +4363,13 @@
         </is>
       </c>
       <c r="D88" t="n">
-        <v>82923499.78135967</v>
+        <v>128456444.0232487</v>
       </c>
       <c r="E88" t="n">
-        <v>81434169.65732384</v>
+        <v>126782789.8757949</v>
       </c>
       <c r="F88" t="n">
-        <v>83395395.81188011</v>
+        <v>129002827.7404833</v>
       </c>
       <c r="G88" t="inlineStr">
         <is>
@@ -4382,7 +4382,7 @@
         </is>
       </c>
       <c r="I88" t="n">
-        <v>2.351719942645667</v>
+        <v>1.720921861615682</v>
       </c>
     </row>
     <row r="89">
@@ -4392,13 +4392,13 @@
         </is>
       </c>
       <c r="D89" t="n">
-        <v>82923499.78135967</v>
+        <v>128456444.0232487</v>
       </c>
       <c r="E89" t="n">
-        <v>81434169.65732384</v>
+        <v>126782789.8757949</v>
       </c>
       <c r="F89" t="n">
-        <v>83395395.81188011</v>
+        <v>129002827.7404833</v>
       </c>
       <c r="G89" t="inlineStr">
         <is>
@@ -4411,7 +4411,7 @@
         </is>
       </c>
       <c r="I89" t="n">
-        <v>2.351719942645667</v>
+        <v>1.720921861615682</v>
       </c>
     </row>
     <row r="90">
@@ -4503,13 +4503,13 @@
         </is>
       </c>
       <c r="D93" t="n">
-        <v>6472456.821415246</v>
+        <v>-59877978.79859084</v>
       </c>
       <c r="E93" t="n">
-        <v>4549205.326766551</v>
+        <v>-62094246.44893396</v>
       </c>
       <c r="F93" t="n">
-        <v>7374626.935385704</v>
+        <v>-58838358.94426459</v>
       </c>
       <c r="G93" t="inlineStr">
         <is>
@@ -4522,7 +4522,7 @@
         </is>
       </c>
       <c r="I93" t="n">
-        <v>38.31273952397403</v>
+        <v>5.24346085324829</v>
       </c>
     </row>
     <row r="94">
@@ -4532,13 +4532,13 @@
         </is>
       </c>
       <c r="D94" t="n">
-        <v>157766493.4357724</v>
+        <v>266806522.8580489</v>
       </c>
       <c r="E94" t="n">
-        <v>157203692.2653289</v>
+        <v>266243140.8132601</v>
       </c>
       <c r="F94" t="n">
-        <v>157766493.4357724</v>
+        <v>266806522.8580489</v>
       </c>
       <c r="G94" t="inlineStr">
         <is>
@@ -4551,7 +4551,7 @@
         </is>
       </c>
       <c r="I94" t="n">
-        <v>0.3567304807168413</v>
+        <v>0.2111575229697731</v>
       </c>
     </row>
     <row r="95">
@@ -4561,13 +4561,13 @@
         </is>
       </c>
       <c r="D95" t="n">
-        <v>163140686.1178045</v>
+        <v>205662954.3586731</v>
       </c>
       <c r="E95" t="n">
-        <v>160640355.0297017</v>
+        <v>202866850.8575234</v>
       </c>
       <c r="F95" t="n">
-        <v>164030467.5356884</v>
+        <v>206693482.3816381</v>
       </c>
       <c r="G95" t="inlineStr">
         <is>
@@ -4580,7 +4580,7 @@
         </is>
       </c>
       <c r="I95" t="n">
-        <v>2.066757814519487</v>
+        <v>1.851355678960951</v>
       </c>
     </row>
     <row r="96">
@@ -4590,13 +4590,13 @@
         </is>
       </c>
       <c r="D96" t="n">
-        <v>163140686.1178045</v>
+        <v>205662954.3586731</v>
       </c>
       <c r="E96" t="n">
-        <v>160640355.0297017</v>
+        <v>202866850.8575234</v>
       </c>
       <c r="F96" t="n">
-        <v>164030467.5356884</v>
+        <v>206693482.3816381</v>
       </c>
       <c r="G96" t="inlineStr">
         <is>
@@ -4609,7 +4609,7 @@
         </is>
       </c>
       <c r="I96" t="n">
-        <v>2.066757814519487</v>
+        <v>1.851355678960951</v>
       </c>
     </row>
     <row r="97">
@@ -4701,13 +4701,13 @@
         </is>
       </c>
       <c r="D100" t="n">
-        <v>9652820.74308759</v>
+        <v>-56213071.8971622</v>
       </c>
       <c r="E100" t="n">
-        <v>6266437.85353297</v>
+        <v>-60115385.69786781</v>
       </c>
       <c r="F100" t="n">
-        <v>11493125.82599008</v>
+        <v>-54092387.92351282</v>
       </c>
       <c r="G100" t="inlineStr">
         <is>
@@ -4720,7 +4720,7 @@
         </is>
       </c>
       <c r="I100" t="n">
-        <v>45.47664448811388</v>
+        <v>10.01906201621296</v>
       </c>
     </row>
     <row r="101">
@@ -4730,13 +4730,13 @@
         </is>
       </c>
       <c r="D101" t="n">
-        <v>315528355.8304815</v>
+        <v>418140844.1240625</v>
       </c>
       <c r="E101" t="n">
-        <v>314370551.7118335</v>
+        <v>416983786.767262</v>
       </c>
       <c r="F101" t="n">
-        <v>315528355.8304815</v>
+        <v>418140844.1240625</v>
       </c>
       <c r="G101" t="inlineStr">
         <is>
@@ -4749,7 +4749,7 @@
         </is>
       </c>
       <c r="I101" t="n">
-        <v>0.3669413849036394</v>
+        <v>0.2767147417096755</v>
       </c>
     </row>
     <row r="102">
@@ -4759,13 +4759,13 @@
         </is>
       </c>
       <c r="D102" t="n">
-        <v>322738037.6217999</v>
+        <v>359112409.8891277</v>
       </c>
       <c r="E102" t="n">
-        <v>318151702.8485751</v>
+        <v>354004469.5619559</v>
       </c>
       <c r="F102" t="n">
-        <v>324571420.9923706</v>
+        <v>361234506.2450304</v>
       </c>
       <c r="G102" t="inlineStr">
         <is>
@@ -4778,7 +4778,7 @@
         </is>
       </c>
       <c r="I102" t="n">
-        <v>1.977906164432879</v>
+        <v>2.00148007958305</v>
       </c>
     </row>
     <row r="103">
@@ -4788,13 +4788,13 @@
         </is>
       </c>
       <c r="D103" t="n">
-        <v>322738037.6217999</v>
+        <v>359112409.8891277</v>
       </c>
       <c r="E103" t="n">
-        <v>318151702.8485751</v>
+        <v>354004469.5619559</v>
       </c>
       <c r="F103" t="n">
-        <v>324571420.9923706</v>
+        <v>361234506.2450304</v>
       </c>
       <c r="G103" t="inlineStr">
         <is>
@@ -4807,7 +4807,7 @@
         </is>
       </c>
       <c r="I103" t="n">
-        <v>1.977906164432879</v>
+        <v>2.00148007958305</v>
       </c>
     </row>
     <row r="104">
@@ -4904,13 +4904,13 @@
         </is>
       </c>
       <c r="D107" t="n">
-        <v>0</v>
+        <v>-47570307.84000003</v>
       </c>
       <c r="E107" t="n">
-        <v>0</v>
+        <v>-47570307.84000003</v>
       </c>
       <c r="F107" t="n">
-        <v>0</v>
+        <v>-47570307.84000003</v>
       </c>
       <c r="G107" t="inlineStr">
         <is>
@@ -4933,13 +4933,13 @@
         </is>
       </c>
       <c r="D108" t="n">
-        <v>78883246.71788645</v>
+        <v>198235742.4940248</v>
       </c>
       <c r="E108" t="n">
-        <v>78601846.13266468</v>
+        <v>197954051.4716301</v>
       </c>
       <c r="F108" t="n">
-        <v>78883246.71788645</v>
+        <v>198235742.4940248</v>
       </c>
       <c r="G108" t="inlineStr">
         <is>
@@ -4952,7 +4952,7 @@
         </is>
       </c>
       <c r="I108" t="n">
-        <v>0.3567304807168402</v>
+        <v>0.1420990073993079</v>
       </c>
     </row>
     <row r="109">
@@ -4962,13 +4962,13 @@
         </is>
       </c>
       <c r="D109" t="n">
-        <v>78167700.90515041</v>
+        <v>149840872.1662183</v>
       </c>
       <c r="E109" t="n">
-        <v>77880238.50656176</v>
+        <v>149552195.7854834</v>
       </c>
       <c r="F109" t="n">
-        <v>78167700.90515041</v>
+        <v>149840872.1662183</v>
       </c>
       <c r="G109" t="inlineStr">
         <is>
@@ -4981,7 +4981,7 @@
         </is>
       </c>
       <c r="I109" t="n">
-        <v>0.3677508680183232</v>
+        <v>0.1926552992929007</v>
       </c>
     </row>
     <row r="110">
@@ -4991,13 +4991,13 @@
         </is>
       </c>
       <c r="D110" t="n">
-        <v>78167700.90515041</v>
+        <v>149840872.1662183</v>
       </c>
       <c r="E110" t="n">
-        <v>77880238.50656176</v>
+        <v>149552195.7854834</v>
       </c>
       <c r="F110" t="n">
-        <v>78167700.90515041</v>
+        <v>149840872.1662183</v>
       </c>
       <c r="G110" t="inlineStr">
         <is>
@@ -5010,7 +5010,7 @@
         </is>
       </c>
       <c r="I110" t="n">
-        <v>0.3677508680183232</v>
+        <v>0.1926552992929007</v>
       </c>
     </row>
     <row r="111">
@@ -5102,13 +5102,13 @@
         </is>
       </c>
       <c r="D114" t="n">
-        <v>0</v>
+        <v>-47570307.84000003</v>
       </c>
       <c r="E114" t="n">
-        <v>0</v>
+        <v>-47570307.84000003</v>
       </c>
       <c r="F114" t="n">
-        <v>0</v>
+        <v>-47570307.84000003</v>
       </c>
       <c r="G114" t="inlineStr">
         <is>
@@ -5131,13 +5131,13 @@
         </is>
       </c>
       <c r="D115" t="n">
-        <v>157756972.8940516</v>
+        <v>273896125.1275721</v>
       </c>
       <c r="E115" t="n">
-        <v>157169329.620728</v>
+        <v>273309373.3028121</v>
       </c>
       <c r="F115" t="n">
-        <v>157756972.8940516</v>
+        <v>273896125.1275721</v>
       </c>
       <c r="G115" t="inlineStr">
         <is>
@@ -5150,7 +5150,7 @@
         </is>
       </c>
       <c r="I115" t="n">
-        <v>0.3724990804166817</v>
+        <v>0.2142242152884309</v>
       </c>
     </row>
     <row r="116">
@@ -5160,13 +5160,13 @@
         </is>
       </c>
       <c r="D116" t="n">
-        <v>156170236.5299845</v>
+        <v>224497334.3860431</v>
       </c>
       <c r="E116" t="n">
-        <v>155568191.3024335</v>
+        <v>223893986.4035029</v>
       </c>
       <c r="F116" t="n">
-        <v>156173110.5300727</v>
+        <v>224504040.1019135</v>
       </c>
       <c r="G116" t="inlineStr">
         <is>
@@ -5179,7 +5179,7 @@
         </is>
       </c>
       <c r="I116" t="n">
-        <v>0.3873389123044425</v>
+        <v>0.271733951038733</v>
       </c>
     </row>
     <row r="117">
@@ -5189,13 +5189,13 @@
         </is>
       </c>
       <c r="D117" t="n">
-        <v>156170236.5299845</v>
+        <v>224497334.3860431</v>
       </c>
       <c r="E117" t="n">
-        <v>155568191.3024335</v>
+        <v>223893986.4035029</v>
       </c>
       <c r="F117" t="n">
-        <v>156173110.5300727</v>
+        <v>224504040.1019135</v>
       </c>
       <c r="G117" t="inlineStr">
         <is>
@@ -5208,7 +5208,7 @@
         </is>
       </c>
       <c r="I117" t="n">
-        <v>0.3873389123044425</v>
+        <v>0.271733951038733</v>
       </c>
     </row>
     <row r="118">
@@ -5300,13 +5300,13 @@
         </is>
       </c>
       <c r="D121" t="n">
-        <v>0</v>
+        <v>-47570307.84000003</v>
       </c>
       <c r="E121" t="n">
-        <v>0</v>
+        <v>-47570307.84000003</v>
       </c>
       <c r="F121" t="n">
-        <v>0</v>
+        <v>-47570307.84000003</v>
       </c>
       <c r="G121" t="inlineStr">
         <is>
@@ -5329,13 +5329,13 @@
         </is>
       </c>
       <c r="D122" t="n">
-        <v>308458353.0788054</v>
+        <v>418546159.5277047</v>
       </c>
       <c r="E122" t="n">
-        <v>305337138.0045896</v>
+        <v>415526549.8914816</v>
       </c>
       <c r="F122" t="n">
-        <v>309764438.7639151</v>
+        <v>419782031.1613963</v>
       </c>
       <c r="G122" t="inlineStr">
         <is>
@@ -5348,7 +5348,7 @@
         </is>
       </c>
       <c r="I122" t="n">
-        <v>1.429247584710569</v>
+        <v>1.013735928177091</v>
       </c>
     </row>
     <row r="123">
@@ -5358,13 +5358,13 @@
         </is>
       </c>
       <c r="D123" t="n">
-        <v>304639337.9363775</v>
+        <v>366574992.1329951</v>
       </c>
       <c r="E123" t="n">
-        <v>301520324.6918135</v>
+        <v>363557919.7852354</v>
       </c>
       <c r="F123" t="n">
-        <v>305988538.4193945</v>
+        <v>367860547.3011179</v>
       </c>
       <c r="G123" t="inlineStr">
         <is>
@@ -5377,7 +5377,7 @@
         </is>
       </c>
       <c r="I123" t="n">
-        <v>1.460255260102845</v>
+        <v>1.169635490255635</v>
       </c>
     </row>
     <row r="124">
@@ -5387,13 +5387,13 @@
         </is>
       </c>
       <c r="D124" t="n">
-        <v>304639337.9363775</v>
+        <v>366574992.1329951</v>
       </c>
       <c r="E124" t="n">
-        <v>301520324.6918135</v>
+        <v>363557919.7852354</v>
       </c>
       <c r="F124" t="n">
-        <v>305988538.4193945</v>
+        <v>367860547.3011179</v>
       </c>
       <c r="G124" t="inlineStr">
         <is>
@@ -5406,7 +5406,7 @@
         </is>
       </c>
       <c r="I124" t="n">
-        <v>1.460255260102845</v>
+        <v>1.169635490255635</v>
       </c>
     </row>
     <row r="125">
@@ -5701,13 +5701,13 @@
         </is>
       </c>
       <c r="D135" t="n">
-        <v>1414360.012903227</v>
+        <v>2835480.812903227</v>
       </c>
       <c r="E135" t="n">
-        <v>1043192.322580645</v>
+        <v>2512118.43870968</v>
       </c>
       <c r="F135" t="n">
-        <v>1414360.012903227</v>
+        <v>2835480.812903227</v>
       </c>
       <c r="G135" t="inlineStr">
         <is>
@@ -5720,7 +5720,7 @@
         </is>
       </c>
       <c r="I135" t="n">
-        <v>26.24280147461845</v>
+        <v>11.40414608774795</v>
       </c>
     </row>
     <row r="136">
@@ -5730,13 +5730,13 @@
         </is>
       </c>
       <c r="D136" t="n">
-        <v>23715557.01062761</v>
+        <v>22279561.62896263</v>
       </c>
       <c r="E136" t="n">
-        <v>21181957.19322234</v>
+        <v>19622065.81315529</v>
       </c>
       <c r="F136" t="n">
-        <v>25237507.33343017</v>
+        <v>23884897.59634926</v>
       </c>
       <c r="G136" t="inlineStr">
         <is>
@@ -5749,7 +5749,7 @@
         </is>
       </c>
       <c r="I136" t="n">
-        <v>16.06953526204924</v>
+        <v>17.84739401120788</v>
       </c>
     </row>
     <row r="137">
@@ -5759,13 +5759,13 @@
         </is>
       </c>
       <c r="D137" t="n">
-        <v>24423754.05393084</v>
+        <v>24499831.20346586</v>
       </c>
       <c r="E137" t="n">
-        <v>21581951.87274331</v>
+        <v>21573828.58956388</v>
       </c>
       <c r="F137" t="n">
-        <v>25945704.37673339</v>
+        <v>26105167.17085248</v>
       </c>
       <c r="G137" t="inlineStr">
         <is>
@@ -5778,7 +5778,7 @@
         </is>
       </c>
       <c r="I137" t="n">
-        <v>16.8187860334339</v>
+        <v>17.35801403466221</v>
       </c>
     </row>
     <row r="138">
@@ -5788,13 +5788,13 @@
         </is>
       </c>
       <c r="D138" t="n">
-        <v>24423754.05393084</v>
+        <v>24499831.20346586</v>
       </c>
       <c r="E138" t="n">
-        <v>21581951.87274331</v>
+        <v>21573828.58956388</v>
       </c>
       <c r="F138" t="n">
-        <v>25945704.37673339</v>
+        <v>26105167.17085248</v>
       </c>
       <c r="G138" t="inlineStr">
         <is>
@@ -5807,7 +5807,7 @@
         </is>
       </c>
       <c r="I138" t="n">
-        <v>16.8187860334339</v>
+        <v>17.35801403466221</v>
       </c>
     </row>
     <row r="139">
@@ -5899,13 +5899,13 @@
         </is>
       </c>
       <c r="D142" t="n">
-        <v>1414360.012903227</v>
+        <v>2835480.812903227</v>
       </c>
       <c r="E142" t="n">
-        <v>1043192.322580645</v>
+        <v>2512118.43870968</v>
       </c>
       <c r="F142" t="n">
-        <v>1414360.012903227</v>
+        <v>2835480.812903227</v>
       </c>
       <c r="G142" t="inlineStr">
         <is>
@@ -5918,7 +5918,7 @@
         </is>
       </c>
       <c r="I142" t="n">
-        <v>26.24280147461845</v>
+        <v>11.40414608774795</v>
       </c>
     </row>
     <row r="143">
@@ -5928,13 +5928,13 @@
         </is>
       </c>
       <c r="D143" t="n">
-        <v>24660958.77724204</v>
+        <v>23272029.67227682</v>
       </c>
       <c r="E143" t="n">
-        <v>21975745.48019315</v>
+        <v>20452277.86005339</v>
       </c>
       <c r="F143" t="n">
-        <v>25876114.84618873</v>
+        <v>24555709.08009543</v>
       </c>
       <c r="G143" t="inlineStr">
         <is>
@@ -5947,7 +5947,7 @@
         </is>
       </c>
       <c r="I143" t="n">
-        <v>15.07324182621669</v>
+        <v>16.71070139598712</v>
       </c>
     </row>
     <row r="144">
@@ -5957,13 +5957,13 @@
         </is>
       </c>
       <c r="D144" t="n">
-        <v>25369155.82054527</v>
+        <v>25492299.24678005</v>
       </c>
       <c r="E144" t="n">
-        <v>22318994.92381698</v>
+        <v>22354604.02147019</v>
       </c>
       <c r="F144" t="n">
-        <v>26584311.88949196</v>
+        <v>26775978.65459865</v>
       </c>
       <c r="G144" t="inlineStr">
         <is>
@@ -5976,7 +5976,7 @@
         </is>
       </c>
       <c r="I144" t="n">
-        <v>16.04448888278708</v>
+        <v>16.51246697707205</v>
       </c>
     </row>
     <row r="145">
@@ -5986,13 +5986,13 @@
         </is>
       </c>
       <c r="D145" t="n">
-        <v>25369155.82054527</v>
+        <v>25492299.24678005</v>
       </c>
       <c r="E145" t="n">
-        <v>22318994.92381698</v>
+        <v>22354604.02147019</v>
       </c>
       <c r="F145" t="n">
-        <v>26584311.88949196</v>
+        <v>26775978.65459865</v>
       </c>
       <c r="G145" t="inlineStr">
         <is>
@@ -6005,7 +6005,7 @@
         </is>
       </c>
       <c r="I145" t="n">
-        <v>16.04448888278708</v>
+        <v>16.51246697707205</v>
       </c>
     </row>
     <row r="146">
@@ -9275,7 +9275,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>10.0 초</t>
+          <t>25.0 초</t>
         </is>
       </c>
     </row>
@@ -9287,7 +9287,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>11.5 초</t>
+          <t>24.7 초</t>
         </is>
       </c>
     </row>
@@ -9299,7 +9299,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>6.8 초</t>
+          <t>16.1 초</t>
         </is>
       </c>
     </row>
@@ -9311,7 +9311,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>11.3 초</t>
+          <t>25.4 초</t>
         </is>
       </c>
     </row>
@@ -9323,7 +9323,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>13.0 초</t>
+          <t>26.2 초</t>
         </is>
       </c>
     </row>
@@ -9335,7 +9335,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>8.1 초</t>
+          <t>20.2 초</t>
         </is>
       </c>
     </row>
@@ -9347,7 +9347,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>14.3 초</t>
+          <t>34.1 초</t>
         </is>
       </c>
     </row>
@@ -9359,7 +9359,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>78.9 초</t>
+          <t>178.0 초</t>
         </is>
       </c>
     </row>

--- a/output/casestudy_20260904.xlsx
+++ b/output/casestudy_20260904.xlsx
@@ -544,7 +544,7 @@
         </is>
       </c>
       <c r="N2" t="n">
-        <v>24.96197000006214</v>
+        <v>22.81403999985196</v>
       </c>
     </row>
     <row r="3">
@@ -596,7 +596,7 @@
         </is>
       </c>
       <c r="N3" t="n">
-        <v>24.71146219992079</v>
+        <v>22.99154740013182</v>
       </c>
     </row>
     <row r="4">
@@ -648,7 +648,7 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>16.12875450006686</v>
+        <v>15.10770759987645</v>
       </c>
     </row>
     <row r="5">
@@ -700,7 +700,7 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>25.42400019988418</v>
+        <v>23.72076880000532</v>
       </c>
     </row>
     <row r="6">
@@ -752,7 +752,7 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>26.2417592999991</v>
+        <v>25.64121360005811</v>
       </c>
     </row>
     <row r="7">
@@ -804,7 +804,7 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>20.21679410012439</v>
+        <v>19.70227249991149</v>
       </c>
     </row>
     <row r="8">
@@ -856,7 +856,7 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>34.05034240009263</v>
+        <v>33.14830380002968</v>
       </c>
     </row>
   </sheetData>
@@ -9275,7 +9275,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>25.0 초</t>
+          <t>22.8 초</t>
         </is>
       </c>
     </row>
@@ -9287,7 +9287,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>24.7 초</t>
+          <t>23.0 초</t>
         </is>
       </c>
     </row>
@@ -9299,7 +9299,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>16.1 초</t>
+          <t>15.1 초</t>
         </is>
       </c>
     </row>
@@ -9311,7 +9311,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>25.4 초</t>
+          <t>23.7 초</t>
         </is>
       </c>
     </row>
@@ -9323,7 +9323,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>26.2 초</t>
+          <t>25.6 초</t>
         </is>
       </c>
     </row>
@@ -9335,7 +9335,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>20.2 초</t>
+          <t>19.7 초</t>
         </is>
       </c>
     </row>
@@ -9347,7 +9347,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>34.1 초</t>
+          <t>33.1 초</t>
         </is>
       </c>
     </row>
@@ -9359,7 +9359,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>178.0 초</t>
+          <t>171.3 초</t>
         </is>
       </c>
     </row>

--- a/output/casestudy_20260904.xlsx
+++ b/output/casestudy_20260904.xlsx
@@ -544,7 +544,7 @@
         </is>
       </c>
       <c r="N2" t="n">
-        <v>22.81403999985196</v>
+        <v>24.38035920006223</v>
       </c>
     </row>
     <row r="3">
@@ -596,7 +596,7 @@
         </is>
       </c>
       <c r="N3" t="n">
-        <v>22.99154740013182</v>
+        <v>24.72537290002219</v>
       </c>
     </row>
     <row r="4">
@@ -648,7 +648,7 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>15.10770759987645</v>
+        <v>16.34663990000263</v>
       </c>
     </row>
     <row r="5">
@@ -700,7 +700,7 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>23.72076880000532</v>
+        <v>25.50479230005294</v>
       </c>
     </row>
     <row r="6">
@@ -752,7 +752,7 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>25.64121360005811</v>
+        <v>27.53974050004035</v>
       </c>
     </row>
     <row r="7">
@@ -804,7 +804,7 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>19.70227249991149</v>
+        <v>21.23814329993911</v>
       </c>
     </row>
     <row r="8">
@@ -856,7 +856,7 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>33.14830380002968</v>
+        <v>35.62893970008008</v>
       </c>
     </row>
   </sheetData>
@@ -9275,7 +9275,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>22.8 초</t>
+          <t>24.4 초</t>
         </is>
       </c>
     </row>
@@ -9287,7 +9287,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>23.0 초</t>
+          <t>24.7 초</t>
         </is>
       </c>
     </row>
@@ -9299,7 +9299,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>15.1 초</t>
+          <t>16.3 초</t>
         </is>
       </c>
     </row>
@@ -9311,7 +9311,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>23.7 초</t>
+          <t>25.5 초</t>
         </is>
       </c>
     </row>
@@ -9323,7 +9323,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>25.6 초</t>
+          <t>27.5 초</t>
         </is>
       </c>
     </row>
@@ -9335,7 +9335,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>19.7 초</t>
+          <t>21.2 초</t>
         </is>
       </c>
     </row>
@@ -9347,7 +9347,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>33.1 초</t>
+          <t>35.6 초</t>
         </is>
       </c>
     </row>
@@ -9359,7 +9359,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>171.3 초</t>
+          <t>181.6 초</t>
         </is>
       </c>
     </row>

--- a/output/casestudy_20260904.xlsx
+++ b/output/casestudy_20260904.xlsx
@@ -544,7 +544,7 @@
         </is>
       </c>
       <c r="N2" t="n">
-        <v>24.38035920006223</v>
+        <v>23.0194574999623</v>
       </c>
     </row>
     <row r="3">
@@ -596,7 +596,7 @@
         </is>
       </c>
       <c r="N3" t="n">
-        <v>24.72537290002219</v>
+        <v>23.24179630004801</v>
       </c>
     </row>
     <row r="4">
@@ -648,7 +648,7 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>16.34663990000263</v>
+        <v>15.28468719986267</v>
       </c>
     </row>
     <row r="5">
@@ -700,7 +700,7 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>25.50479230005294</v>
+        <v>23.91559969983064</v>
       </c>
     </row>
     <row r="6">
@@ -752,7 +752,7 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>27.53974050004035</v>
+        <v>25.82671070005745</v>
       </c>
     </row>
     <row r="7">
@@ -804,7 +804,7 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>21.23814329993911</v>
+        <v>19.9512473999057</v>
       </c>
     </row>
     <row r="8">
@@ -856,7 +856,7 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>35.62893970008008</v>
+        <v>33.1695902000647</v>
       </c>
     </row>
   </sheetData>
@@ -9275,7 +9275,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>24.4 초</t>
+          <t>23.0 초</t>
         </is>
       </c>
     </row>
@@ -9287,7 +9287,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>24.7 초</t>
+          <t>23.2 초</t>
         </is>
       </c>
     </row>
@@ -9299,7 +9299,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>16.3 초</t>
+          <t>15.3 초</t>
         </is>
       </c>
     </row>
@@ -9311,7 +9311,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>25.5 초</t>
+          <t>23.9 초</t>
         </is>
       </c>
     </row>
@@ -9323,7 +9323,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>27.5 초</t>
+          <t>25.8 초</t>
         </is>
       </c>
     </row>
@@ -9335,7 +9335,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>21.2 초</t>
+          <t>20.0 초</t>
         </is>
       </c>
     </row>
@@ -9347,7 +9347,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>35.6 초</t>
+          <t>33.2 초</t>
         </is>
       </c>
     </row>
@@ -9359,7 +9359,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>181.6 초</t>
+          <t>170.2 초</t>
         </is>
       </c>
     </row>
